--- a/data/Risk Taxonomy.xlsx
+++ b/data/Risk Taxonomy.xlsx
@@ -17,98 +17,140 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="lt9aDOqjDXXks14aXxG16wqL0rcYlreOxcEjPJ9T4Cc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="0kNBUqG3l8HDyybO04tQrcWzwWIDKLzxWJYC/KLlBas="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="350">
-  <si>
-    <t>QUY ƯỚC</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="418">
   <si>
     <t>BẢNG PHÂN LOẠI RỦI RO TRONG HỢP ĐỒNG THUÊ NHÀ
 (RISK TAXONOMY)</t>
   </si>
   <si>
+    <t>1, NHÓM CHỦ THỂ &amp; THẨM QUYỀN (ENTITY &amp; AUTHORITY)</t>
+  </si>
+  <si>
+    <t>2, NHÓM ĐẶT CỌC &amp; THỎA THUẬN TIỀN THUÊ (DEPOSIT &amp; PAYMENT)</t>
+  </si>
+  <si>
+    <t>QUY ƯỚC</t>
+  </si>
+  <si>
+    <t>Mã</t>
+  </si>
+  <si>
+    <t>Tên</t>
+  </si>
+  <si>
+    <t>Mức độ</t>
+  </si>
+  <si>
+    <t>Dấu hiệu nhận biết</t>
+  </si>
+  <si>
+    <t>Căn cứ pháp lý</t>
+  </si>
+  <si>
+    <t>Rủi ro thực tế</t>
+  </si>
+  <si>
     <t>Mức độ rủi ro:</t>
   </si>
   <si>
+    <t>Nhãn</t>
+  </si>
+  <si>
     <t xml:space="preserve">            1. LOW:</t>
   </si>
   <si>
+    <t>A - DEP - 01</t>
+  </si>
+  <si>
     <t xml:space="preserve">                        Thiếu sót thủ tục hành chính, quy trình chưa rõ ràng</t>
   </si>
   <si>
+    <t>A - AUT - 01</t>
+  </si>
+  <si>
+    <t>Tiền đặt cọc được gắn với nghĩa vụ trái pháp luật</t>
+  </si>
+  <si>
+    <t>Cho thuê nhà khi không có quyền/thẩm quyền</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>Cọc dùng để bảo đảm một nghĩa vụ hoặc mục đích mà pháp luật không công nhận</t>
+  </si>
+  <si>
+    <t>Bên A không phải chủ sở hữu và không có căn cứ chứng minh quyền cho thuê</t>
+  </si>
+  <si>
+    <t>Điều 117, 123, 328 BLDS 2015</t>
+  </si>
+  <si>
+    <t>Điều 117, 141, 142 BLDS 2015</t>
+  </si>
+  <si>
+    <t>Thỏa thuận có nguy cơ bị vô hiệu, gây mất hoặc khó thu hồi tiền</t>
+  </si>
+  <si>
     <t xml:space="preserve">            2. MEDIUM:</t>
   </si>
   <si>
+    <t>DEPOSIT, ILLEGAL, OBLIGATION</t>
+  </si>
+  <si>
+    <t>A - DEP - 02</t>
+  </si>
+  <si>
     <t xml:space="preserve">                        Quy trình vận hành mập mờ, dễ phát sinh tranh chấp (chi phí, bảo trì)</t>
   </si>
   <si>
+    <t>Giữ/Khấu trừ tiền cọc không có căn cứ</t>
+  </si>
+  <si>
     <t xml:space="preserve">            3. HIGH:</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Cho phép giữ/khấu trừ tiền cọc trong những trường hợp không có căn cứ</t>
+  </si>
+  <si>
+    <t>Điều 328 BLDS 2015</t>
+  </si>
+  <si>
+    <t>Phái hoàn trả tiền cọc cho bên B, phát sinh tranh chấp</t>
+  </si>
+  <si>
     <t xml:space="preserve">                        Gây thiệt hại đáng kể về tài chính, mất lợi thế khi tranh chấp, bị áp đặt các nghĩa vụ vô lý</t>
   </si>
   <si>
+    <t>DEPOSIT, DEDUCTION, FOUNDATION, BASED</t>
+  </si>
+  <si>
+    <t>A - DEP - 03</t>
+  </si>
+  <si>
+    <t>Xử lý tiền cọc không phù hợp khi bên thuê vi phạm</t>
+  </si>
+  <si>
     <t xml:space="preserve">            4. CRITICAL:</t>
   </si>
   <si>
-    <t xml:space="preserve">                        Gây tổn thất về tài chính ngay lập tức, bất ngờ mất quyền sử dụng, hoặc vi phạm pháp luật nghiêm trọng</t>
-  </si>
-  <si>
-    <t>Bên A: Cho thuê</t>
-  </si>
-  <si>
-    <t>Mã A: Rủi ro đối với người cho thuê</t>
-  </si>
-  <si>
-    <t>Bên B: Thuê</t>
-  </si>
-  <si>
-    <t>Mã B: Rủi ro đối với người thuê</t>
-  </si>
-  <si>
-    <t>1, NHÓM CHỦ THỂ &amp; THẨM QUYỀN (ENTITY &amp; AUTHORITY)</t>
-  </si>
-  <si>
-    <t>Mã</t>
-  </si>
-  <si>
-    <t>Tên</t>
-  </si>
-  <si>
-    <t>Mức độ</t>
-  </si>
-  <si>
-    <t>Dấu hiệu nhận biết</t>
-  </si>
-  <si>
-    <t>Căn cứ pháp lý</t>
-  </si>
-  <si>
-    <t>Rủi ro thực tế</t>
-  </si>
-  <si>
-    <t>Nhãn</t>
-  </si>
-  <si>
-    <t>A - AUT - 01</t>
-  </si>
-  <si>
-    <t>Cho thuê nhà khi không có quyền/thẩm quyền</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>Bên A không phải chủ sở hữu và không có căn cứ chứng minh quyền cho thuê</t>
-  </si>
-  <si>
-    <t>Điều 117, 141, 142 BLDS 2015</t>
+    <t>Tự động giữ toàn bộ cọc cho mọi trường hợp bên B vi phạm</t>
+  </si>
+  <si>
+    <t>Có thể không được công nhận toàn bộ quyền giữ tiền cọc</t>
+  </si>
+  <si>
+    <t>DEPOSIT, HANDLING, VIOLATION</t>
   </si>
   <si>
     <t>Hợp đồng không ràng buộc được chủ sở hữu
@@ -116,42 +158,111 @@
 Phát sinh tranh chấp và yêu cầu chấm dứt/hoàn trả</t>
   </si>
   <si>
-    <t>THAM_QUYEN, SO_HUU, CHUNG_MINH</t>
+    <t>A - DEP - 04</t>
+  </si>
+  <si>
+    <t>Không hoàn trả cọc khi nghĩa vụ hoàn trả đã phát sinh</t>
+  </si>
+  <si>
+    <t>Nghĩa vụ bảo đảm đã hoàn thành nhưng vẫn giữ cọc</t>
+  </si>
+  <si>
+    <t>LEGAL_AUTHORITY, OWNERSHIP, PROOF</t>
+  </si>
+  <si>
+    <t>Vẫn phải hoàn trả cọc, có thể phát sinh trách nhiệm do chậm trả</t>
+  </si>
+  <si>
+    <t>REFUND, OBLIGATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        Gây tổn thất về tài chính ngay lập tức, bất ngờ mất quyền sử dụng, hoặc vi phạm pháp luật nghiêm trọng</t>
   </si>
   <si>
     <t>A - AUT - 02</t>
   </si>
   <si>
+    <t>A - DEP - 05</t>
+  </si>
+  <si>
+    <t>Quyền thay đổi tiền thuê không có căn cứ</t>
+  </si>
+  <si>
     <t>Cho thuê tải sản chung nhưng thiếu ủy quyền cần thiết</t>
   </si>
   <si>
-    <t>HIGH</t>
+    <t>Cho phép tự ý tăng giá không theo thỏa thuận/căn cứ pháp luật</t>
+  </si>
+  <si>
+    <t>Điều 68, 72 Luật Kinh doanh bất động sản 2023</t>
+  </si>
+  <si>
+    <t>Tranh chấp về giá thuê, khó thực thi mức giá mới</t>
+  </si>
+  <si>
+    <t>PAYMENT, FOUNDATION, BASED</t>
   </si>
   <si>
     <t>Bên A không có quyền đại diện tất cả đồng sở hữu của nhà cho thuê</t>
+  </si>
+  <si>
+    <t>A -DEP - 06</t>
+  </si>
+  <si>
+    <t>Lãi/Phạt chậm thanh toán không phù hợp</t>
   </si>
   <si>
     <t>Điều 212, 213 BLDS 2015
 Điều 11 Luật Nhà ở 2023</t>
   </si>
   <si>
-    <t>2, NHÓM ĐẶT CỌC &amp; THỎA THUẬN TIỀN THUÊ (DEPOSIT &amp; PAYMENT)</t>
+    <t>Mức hoặc cách tính không phù hợp với pháp luật</t>
+  </si>
+  <si>
+    <t>Điều 357, 418, 468 BLDS 2015</t>
+  </si>
+  <si>
+    <t>Khoản lãi/phạt có thể không được công nhận</t>
+  </si>
+  <si>
+    <t>PAYMENT, PENALTY</t>
   </si>
   <si>
     <t>Tranh chấp với đồng sở hữu
 Hợp đồng không ràng buộc được đầy đủ các chủ thể có thẩm quyền</t>
   </si>
   <si>
-    <t>UY_QUYEN, DAI_DIEN, DONG_SO_HUU</t>
+    <t>A - DEP - 07</t>
+  </si>
+  <si>
+    <t>Yêu cầu khoản thanh toán không có căn cứ</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION, REPRESENTATION, JOINT_OWNERSHIP</t>
+  </si>
+  <si>
+    <t>Thu khoản tiền không xác định rõ nghĩa vụ/căn cứ</t>
+  </si>
+  <si>
+    <t>Điều 3, 4, 385, 398 BLDS 2015</t>
   </si>
   <si>
     <t>A - AUT - 03</t>
   </si>
   <si>
+    <t>Không thu được khoản tiền, phát sinh tranh chấp</t>
+  </si>
+  <si>
+    <t>PAYMENT, REQUEST, OBLIGATION, FOUNDATION</t>
+  </si>
+  <si>
     <t>Người cho thuê không đủ năng lực chủ thể để xác lập giao dịch</t>
   </si>
   <si>
     <t>Bên A (dù có quyền/thẩm quyền) là người chưa thành niên/người mất năng lực nhưng không có đại diện phù hợp</t>
+  </si>
+  <si>
+    <t>A - DEP - 08</t>
   </si>
   <si>
     <t>Điều 117, 122, 125 BLDS 2015
@@ -162,7 +273,10 @@
 Phát sinh hoàn trả và bồi thường</t>
   </si>
   <si>
-    <t>NANG_LUC_CHU_THE, DAI_DIEN</t>
+    <t>LEGAL_CAPACITY, MINOR, REPRESENTATION</t>
+  </si>
+  <si>
+    <t>Quy định tiền thuê không đủ rõ để yêu cầu thanh toán</t>
   </si>
   <si>
     <t>A - AUT - 04</t>
@@ -174,279 +288,183 @@
     <t>MEDIUM</t>
   </si>
   <si>
+    <t>Không xác định rõ giá thuê/kỳ/phương thức thanh toán</t>
+  </si>
+  <si>
+    <t>Điều 398 BLDS 2015, Điều 14 Bộ luật Kinh doanh bất động sản 2023</t>
+  </si>
+  <si>
     <t>Nhà đang trong thời hạn sở hữu không còn phù hợp, thuộc diện bị thu hồi hoặc không đảm bảo điều kiện tối thiểu khi cho thuê</t>
   </si>
   <si>
+    <t>Bên A: Cho thuê</t>
+  </si>
+  <si>
     <t>Điều 160 Luật Nhà ở 2023</t>
+  </si>
+  <si>
+    <t>Khó chứng minh và yêu cầu thanh toán</t>
   </si>
   <si>
     <t>Hợp đồng có nguy cơ xảy ra tranh chấp
 Phải chấm dứt, hoàn trả và bồi thường thiệt hại nếu có</t>
   </si>
   <si>
-    <t>THU_HOI, TRANH_CHAP</t>
+    <t>ELIGIBILITY, RECALL, REQUIREMENT</t>
+  </si>
+  <si>
+    <t>INFORMATION, PAYMENT, CLARITY</t>
   </si>
   <si>
     <t>A - AUT - 05</t>
   </si>
   <si>
-    <t>A - DEP - 01</t>
-  </si>
-  <si>
-    <t>Tiền đặt cọc được gắn với nghĩa vụ trái pháp luật</t>
+    <t>B - DEP - 01</t>
+  </si>
+  <si>
+    <t>Tiền đặt cọc được dùng để bảo đảm nghĩa vụ trái pháp luật</t>
   </si>
   <si>
     <t>Thông tin chủ thể/quyền cho thuê/ủy quyền ghi nhận không đầy đủ</t>
   </si>
   <si>
-    <t>Cọc dùng để bảo đảm một nghĩa vụ hoặc mục đích mà pháp luật không công nhận</t>
-  </si>
-  <si>
-    <t>Điều 117, 123, 328 BLDS 2015</t>
+    <t>Mã A: Rủi ro đối với người cho thuê</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>Thỏa thuận có nguy cơ bị vô hiệu, gây mất hoặc khó thu hồi tiền</t>
-  </si>
-  <si>
     <t>Bên A không cung cấp đầy đủ thông tin chủ thể ký hợp đồng, quyền hoặc ủy quyền cho thuê từ chủ sở hữu</t>
   </si>
   <si>
     <t>Điều 14 Luật KDBĐS 2023</t>
   </si>
   <si>
-    <t>DAT_COC, NGHIA_VU</t>
+    <t>B - DEP - 02</t>
   </si>
   <si>
     <t>Khó xác minh tư cách chủ thể/quyền cho thuê trong trường hợp phát sinh tranh chấp</t>
   </si>
   <si>
-    <t>A - DEP - 02</t>
-  </si>
-  <si>
-    <t>THONG_TIN, QUYEN, UY_QUYEN, DAI_DIEN</t>
-  </si>
-  <si>
-    <t>Giữ/Khấu trừ tiền cọc không có căn cứ</t>
-  </si>
-  <si>
-    <t>Cho phép giữ/khấu trừ tiền cọc trong những trường hợp không có căn cứ</t>
-  </si>
-  <si>
-    <t>Điều 328 BLDS 2015</t>
+    <t>Nguy cơ mất/khấu trừ tiền cọc không có căn cứ</t>
+  </si>
+  <si>
+    <t>Cho phép bên A giũ/trừ cọc quá rộng</t>
+  </si>
+  <si>
+    <t>INFORMATION, AUTHORITY, AUTHORIZATION, REPRESENTATION</t>
+  </si>
+  <si>
+    <t>Mất một phần/toàn bộ tiền cọc</t>
+  </si>
+  <si>
+    <t>DEPOSIT, DEDUCTION, FOUNDATION</t>
+  </si>
+  <si>
+    <t>Bên B: Thuê</t>
   </si>
   <si>
     <t>B - AUT - 01</t>
   </si>
   <si>
-    <t>Phái hoàn trả tiền cọc cho bên B, phát sinh tranh chấp</t>
+    <t>B - DEP - 03</t>
+  </si>
+  <si>
+    <t>Điều kiện mất cọc không phù hợp với trường hợp vi phạm</t>
   </si>
   <si>
     <t>Thuê từ người không có quyền/thẩm quyền</t>
+  </si>
+  <si>
+    <t>Mất cọc dù chưa đủ căn cứ phát sinh hậu quả</t>
+  </si>
+  <si>
+    <t>Mất cọc hoặc phải tranh chấp để đòi lại</t>
+  </si>
+  <si>
+    <t>DEPOSIT, HANDLING, VIOLATION, BASED</t>
   </si>
   <si>
     <t>Hợp đồng không được chủ sở hữu công nhận
 Nguy cơ phải trả lại nhà</t>
   </si>
   <si>
-    <t>A - DEP - 03</t>
-  </si>
-  <si>
-    <t>Xử lý tiền cọc không phù hợp khi bên thuê vi phạm</t>
-  </si>
-  <si>
-    <t>Tự động giữ toàn bộ cọc cho mọi trường hợp bên B vi phạm</t>
+    <t>B - DEP - 04</t>
+  </si>
+  <si>
+    <t>Không có cơ chế rõ ràng để hoàn trả tiền cọc</t>
   </si>
   <si>
     <t>B - AUT - 02</t>
   </si>
   <si>
-    <t>Có thể không được công nhận toàn bộ quyền giữ tiền cọc</t>
+    <t>Không xác định rõ thời điểm/điều kiện hoàn cọc</t>
+  </si>
+  <si>
+    <t>Mã B: Rủi ro đối với người thuê</t>
   </si>
   <si>
     <t>Thuê tài sản chung mà không đầy đủ ủy quyền</t>
   </si>
   <si>
-    <t>XU_LY_COC</t>
-  </si>
-  <si>
-    <t>A - DEP - 04</t>
-  </si>
-  <si>
-    <t>Không hoàn trả cọc khi nghĩa vụ hoàn trả đã phát sinh</t>
+    <t>Khó thu hồi cọc, dễ phát sinh tranh chấp</t>
+  </si>
+  <si>
+    <t>B - DEP - 05</t>
+  </si>
+  <si>
+    <t>Quyền tăng tiền thuê đơn phương</t>
   </si>
   <si>
     <t>Tranh chấp với đồng sở hữu
 Hợp đồng không được thực hiện ổn định</t>
   </si>
   <si>
-    <t>Nghĩa vụ bảo đảm đã hoàn thành nhưng vẫn giữ cọc</t>
-  </si>
-  <si>
-    <t>Vẫn phải hoàn trả cọc, có thể phát sinh trách nhiệm do chậm trả</t>
-  </si>
-  <si>
-    <t>KHONG_HOAN_TRA_COC</t>
-  </si>
-  <si>
-    <t>A - DEP - 05</t>
+    <t>Bên A được tự quyêt định tăng giá</t>
+  </si>
+  <si>
+    <t>Phải đối mặt với yêu cầu tăng giá hoặc tranh chấp</t>
   </si>
   <si>
     <t>B - AUT - 03</t>
   </si>
   <si>
-    <t>Quyền thay đổi tiền thuê không có căn cứ</t>
-  </si>
-  <si>
     <t>Thuê nhà từ người không đủ năng lực chủ thể để xác lập giao dịch</t>
-  </si>
-  <si>
-    <t>Cho phép tự ý tăng giá không theo thỏa thuận/căn cứ pháp luật</t>
-  </si>
-  <si>
-    <t>Điều 68, 72 Luật Kinh doanh bất động sản 2023</t>
-  </si>
-  <si>
-    <t>Tranh chấp về giá thuê, khó thực thi mức giá mới</t>
   </si>
   <si>
     <t>Điều 117, 122, 125 BLDS 2015
 Điều 161 Luật Nhà ở 2013</t>
   </si>
   <si>
-    <t>A -DEP - 06</t>
-  </si>
-  <si>
     <t>Hợp đồng bị vô hiệu
 Nguy cơ phải trả lại nhà</t>
   </si>
   <si>
-    <t>Lãi/Phạt chậm thanh toán không phù hợp</t>
-  </si>
-  <si>
-    <t>Mức hoặc cách tính không phù hợp với pháp luật</t>
-  </si>
-  <si>
     <t>B - AUT - 04</t>
   </si>
   <si>
-    <t>Điều 357, 418, 468 BLDS 2015</t>
-  </si>
-  <si>
-    <t>Khoản lãi/phạt có thể không được công nhận</t>
-  </si>
-  <si>
-    <t>A - DEP - 07</t>
+    <t>PAYMENT, FOUNDATION</t>
   </si>
   <si>
     <t>Nhà đang trong thời hạn sở hữu không còn phù hợp, thuộc diện bị thu hồi hoặc không đảm bảo điều kiện tối thiểu để thuê</t>
   </si>
   <si>
-    <t>Yêu cầu khoản thanh toán không có căn cứ</t>
+    <t>B - DEP - 06</t>
   </si>
   <si>
     <t>Gián đoạn quyền sử dụng nhà
 Nguy cơ phải chấm dứt hợp đồng</t>
   </si>
   <si>
-    <t>Thu khoản tiền không xác định rõ nghĩa vụ/căn cứ</t>
-  </si>
-  <si>
-    <t>Điều 3, 4, 385, 398 BLDS 2015</t>
-  </si>
-  <si>
-    <t>Không thu được khoản tiền, phát sinh tranh chấp</t>
+    <t>Mức lãi/phạt quá mức hoặc chồng nhiều chế tài</t>
+  </si>
+  <si>
+    <t>Có nguy cơ phải chịu khoản tiền không được pháp luật công nhận</t>
   </si>
   <si>
     <t>B - AUT - 05</t>
   </si>
   <si>
-    <t>THU_TIEN_KHONG_CAN_CU</t>
-  </si>
-  <si>
-    <t>A - DEP - 08</t>
-  </si>
-  <si>
-    <t>Quy định tiền thuê không đủ rõ để yêu cầu thanh toán</t>
-  </si>
-  <si>
-    <t>Không xác định rõ giá thuê/kỳ/phương thức thanh toán</t>
-  </si>
-  <si>
-    <t>Điều 398 BLDS 2015, Điều 14 Bộ luật Kinh doanh bất động sản 2023</t>
-  </si>
-  <si>
-    <t>Khó chứng minh và yêu cầu thanh toán</t>
-  </si>
-  <si>
-    <t>KHONG_XAC_DINH</t>
-  </si>
-  <si>
-    <t>B - DEP - 01</t>
-  </si>
-  <si>
-    <t>Tiền đặt cọc được dùng để bảo đảm nghĩa vụ trái pháp luật</t>
-  </si>
-  <si>
-    <t>B - DEP - 02</t>
-  </si>
-  <si>
-    <t>Nguy cơ mất/khấu trừ tiền cọc không có căn cứ</t>
-  </si>
-  <si>
-    <t>Cho phép bên A giũ/trừ cọc quá rộng</t>
-  </si>
-  <si>
-    <t>Mất một phần/toàn bộ tiền cọc</t>
-  </si>
-  <si>
-    <t>B - DEP - 03</t>
-  </si>
-  <si>
-    <t>Điều kiện mất cọc không phù hợp với trường hợp vi phạm</t>
-  </si>
-  <si>
-    <t>Mất cọc dù chưa đủ căn cứ phát sinh hậu quả</t>
-  </si>
-  <si>
-    <t>Mất cọc hoặc phải tranh chấp để đòi lại</t>
-  </si>
-  <si>
-    <t>B - DEP - 04</t>
-  </si>
-  <si>
-    <t>Không có cơ chế rõ ràng để hoàn trả tiền cọc</t>
-  </si>
-  <si>
-    <t>Không xác định rõ thời điểm/điều kiện hoàn cọc</t>
-  </si>
-  <si>
-    <t>Khó thu hồi cọc, dễ phát sinh tranh chấp</t>
-  </si>
-  <si>
-    <t>B - DEP - 05</t>
-  </si>
-  <si>
-    <t>Quyền tăng tiền thuê đơn phương</t>
-  </si>
-  <si>
-    <t>Bên A được tự quyêt định tăng giá</t>
-  </si>
-  <si>
-    <t>Phải đối mặt với yêu cầu tăng giá hoặc tranh chấp</t>
-  </si>
-  <si>
-    <t>B - DEP - 06</t>
-  </si>
-  <si>
-    <t>Mức lãi/phạt quá mức hoặc chồng nhiều chế tài</t>
-  </si>
-  <si>
-    <t>Có nguy cơ phải chịu khoản tiền không được pháp luật công nhận</t>
-  </si>
-  <si>
     <t>B - DEP - 07</t>
   </si>
   <si>
@@ -489,6 +507,9 @@
     <t xml:space="preserve">Bên B có thể yêu cầu sửa chữa, giảm giá thuê hoạc chấm dữt và đòi bồi thường trong trường hợp luật định </t>
   </si>
   <si>
+    <t>REPAIR, RESPONSIBILITY, DAMAGE, DEFECTS</t>
+  </si>
+  <si>
     <t>A - MNT - 02</t>
   </si>
   <si>
@@ -498,12 +519,15 @@
     <t>Cho phép cải tạo mà không cần sự đồng ý của bên B, trừ trường hợp ngoại lệ</t>
   </si>
   <si>
-    <t>Điều 32, 72 Luật KDBĐS 2023</t>
+    <t>Điều 132, 72 Luật KDBĐS 2023</t>
   </si>
   <si>
     <t>Phát sinh tranh chấp, bên A có thể phải chịu trách nhiệm đối với thiệt hại/quyền của bên B</t>
   </si>
   <si>
+    <t>MAINTENANCE, REPAIR, AGREEMENT</t>
+  </si>
+  <si>
     <t>A - MNT - 03</t>
   </si>
   <si>
@@ -519,10 +543,13 @@
     <t>Phải thanh toán chi phí hợp lý, phát sinh tranh chấp</t>
   </si>
   <si>
+    <t>PAYMENT, MAINTENANCE, OBLIGATION</t>
+  </si>
+  <si>
     <t>A - MNT - 04</t>
   </si>
   <si>
-    <t>Điều chỉnh giá thuê sau khi cải tạo không đúng điều kiện</t>
+    <t>Điều chỉnh giá thuê sau cải tạo không đúng điều kiện</t>
   </si>
   <si>
     <t>Cho phép tăng giá bất kỳ lúc nào sau cải tạo</t>
@@ -534,18 +561,24 @@
     <t>Việc tăng giá có thể bị tranh chấp, bên B có quyền chấm dứt trong trường hợp luật định</t>
   </si>
   <si>
+    <t>PAYMENT, ADJUSTMENT</t>
+  </si>
+  <si>
     <t>A - MNT - 05</t>
   </si>
   <si>
     <t>Không duy trì tài sản đúng tình trạng và mục đích thuê</t>
   </si>
   <si>
-    <t>Không bảo đảm tài sản tiếp tục phù hợp với thỏa thuậ/mục đích thuê</t>
+    <t>Không bảo đảm tài sản tiếp tục phù hợp với thỏa thuận/mục đích thuê</t>
   </si>
   <si>
     <t>Bên B có thể yêu cầu sửa chữa, giảm giá thuê hoặc áp dụng quyền chấm dứt theo luật</t>
   </si>
   <si>
+    <t>PURPOSE, MAINTENANCE</t>
+  </si>
+  <si>
     <t>B - MNT - 01</t>
   </si>
   <si>
@@ -556,6 +589,9 @@
   </si>
   <si>
     <t>Phải chịu chi phí không thuộc trách nhiệm của mình, khó yêu cầu chủ nhà sửa chữa</t>
+  </si>
+  <si>
+    <t>REPAIR, RESPONSIBILITY, DAMAGE, DEFECTS, NATURAL_DAMAGE</t>
   </si>
   <si>
     <t>B - MNT - 02</t>
@@ -589,6 +625,9 @@
     <t>Mất quyền sử dụng tương ứng nhưng vẫn phải chịu chi phí thuê, tranh chấp hờn tiền/gia hạn</t>
   </si>
   <si>
+    <t>PAYMENT, PERIOD, INTERRUPTION</t>
+  </si>
+  <si>
     <t>B - MNT - 04</t>
   </si>
   <si>
@@ -599,6 +638,9 @@
   </si>
   <si>
     <t>Khó bảo vệ quyền sửa chữa, yêu cầu giảm giá thuê hoặc hoàn chi phí</t>
+  </si>
+  <si>
+    <t>REPAIR, REQUEST, REFUND</t>
   </si>
   <si>
     <t>4, THỜI GIAN, GIA HẠN, CHẤM DỨT &amp; HOÀN TRẢ TÀI SẢN (EXTENSION &amp; TERMINATION)</t>
@@ -621,6 +663,9 @@
 Phải bồi thường thiệt hại nếu có</t>
   </si>
   <si>
+    <t>UNILATERAL, TERMINATION, EVICTION, BASED</t>
+  </si>
+  <si>
     <t>A - TRM - 02</t>
   </si>
   <si>
@@ -637,6 +682,9 @@
 Không thu hồi được nhà như dự kiến</t>
   </si>
   <si>
+    <t>CONTINUITY, OWNERSHIP, EVICTION</t>
+  </si>
+  <si>
     <t>A - TRM - 03</t>
   </si>
   <si>
@@ -652,6 +700,9 @@
     <t>Tranh chấp về thời điểm chấm dứt và quyền yêu cầu trả nhà</t>
   </si>
   <si>
+    <t>INFORMATION, CLARITY, EVICTION, CONTINUITY</t>
+  </si>
+  <si>
     <t>A - TRM - 04</t>
   </si>
   <si>
@@ -667,6 +718,9 @@
     <t>Yêu cầu bồi thường có thể không được chấp nhận</t>
   </si>
   <si>
+    <t>COMPENSATION, NATURAL_DAMAGE</t>
+  </si>
+  <si>
     <t>A - TRM - 05</t>
   </si>
   <si>
@@ -680,6 +734,9 @@
   </si>
   <si>
     <t>Khó chứng minh hư hỏng phát sinh trong thời gian thuê để yêu cầu bồi thường</t>
+  </si>
+  <si>
+    <t>STATUS, INFORMATION, CLARITY</t>
   </si>
   <si>
     <t>B - TRM - 01</t>
@@ -695,6 +752,12 @@
 Phát sinh tranh chấp và phải yêu cầu bồi thường</t>
   </si>
   <si>
+    <t>5, VI PHẠM, PHẠT &amp; BỒI THƯỜNG (VIOLENCE &amp; PENALTY)</t>
+  </si>
+  <si>
+    <t>TERMINATION, EVICTION, BASED</t>
+  </si>
+  <si>
     <t>B - TRM - 02</t>
   </si>
   <si>
@@ -717,6 +780,9 @@
 Chịu trách nhiệm khi chấm dứt hợp đồng</t>
   </si>
   <si>
+    <t>UNILATERAL, TERMINATION, RESTRICTION</t>
+  </si>
+  <si>
     <t>B - TRM - 04</t>
   </si>
   <si>
@@ -742,21 +808,18 @@
   </si>
   <si>
     <t>Không xác định rõ hiện trạng và nghĩa vụ hoàn trả tài sản</t>
+  </si>
+  <si>
+    <t>A - PEN - 01</t>
+  </si>
+  <si>
+    <t>Bên thuê chậm thanh toán tiền thuê</t>
   </si>
   <si>
     <t>Không xác định được hư hỏng phát sinh trong thời gian thuê
 Dễ phát sinh tranh chấp/đòi bồi thường</t>
   </si>
   <si>
-    <t>5, VI PHẠM, PHẠT &amp; BỒI THƯỜNG (VIOLENCE &amp; PENALTY)</t>
-  </si>
-  <si>
-    <t>A - PEN - 01</t>
-  </si>
-  <si>
-    <t>Bên thuê chậm thanh toán tiền thuê</t>
-  </si>
-  <si>
     <t>Hợp đồng không quy định rõ thời hạn thanh toán, thời gian gia hạn hoặc cách xử lý khi chậm trả</t>
   </si>
   <si>
@@ -768,6 +831,9 @@
 Phát sinh tranh chấp về nghĩa vụ thanh toán</t>
   </si>
   <si>
+    <t>LATE, PAYMENT, HANDLING</t>
+  </si>
+  <si>
     <t>A - PEN - 02</t>
   </si>
   <si>
@@ -787,6 +853,9 @@
 Phát sinh tranh chấp với bên B do khoản phạt quá thấp</t>
   </si>
   <si>
+    <t>VIOLATION, PENALTY, CLARITY</t>
+  </si>
+  <si>
     <t>A - PEN - 03</t>
   </si>
   <si>
@@ -803,6 +872,9 @@
 Khó chứng minh hư hại để yêu cầu bên A bồi thường</t>
   </si>
   <si>
+    <t>DAMAGE, PROOF, DETERMINATION, VIOLENCE</t>
+  </si>
+  <si>
     <t>A - PEN - 04</t>
   </si>
   <si>
@@ -818,6 +890,9 @@
     <t>Khi trả nhà, chủ nhà yêu cầu người thuê trả tiền thay mới thiết bị đã cũ hoặc sửa chữa hư hỏng có trước khi nhận nhà.</t>
   </si>
   <si>
+    <t>DAMAGE, RESPONSIBILITY, NATURAL_DAMAGE</t>
+  </si>
+  <si>
     <t>A - PEN - 05</t>
   </si>
   <si>
@@ -831,6 +906,9 @@
   </si>
   <si>
     <t>Người thuê bị yêu cầu rời khỏi nhà vì vi phạm nhỏ hoặc chủ nhà chấm dứt hợp đồng khi chưa đáp ứng điều kiện áp dụng.</t>
+  </si>
+  <si>
+    <t>CONDITION, VIOLENCE, TERMINATION, NOTIFICATION</t>
   </si>
   <si>
     <t>A - PEN - 06</t>
@@ -846,7 +924,11 @@
 Điều 172 Luật nhà ở 2023</t>
   </si>
   <si>
-    <t>Chủ nhà cho rằng đã thông báo yêu cầu khắc phục nhưng người thuê phủ nhận; hai bên không thống nhất được thời điểm bắt đầu tính thời hạn xử lý vi phạm.</t>
+    <t>Chủ nhà cho rằng đã thông báo yêu cầu khắc phục nhưng người thuê phủ nhận
+Hai bên không thống nhất được thời điểm bắt đầu tính thời hạn xử lý vi phạm.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION, PROOF, VIOLENCE</t>
   </si>
   <si>
     <t>B - PEN - 01</t>
@@ -862,53 +944,71 @@
 Điều 170 Luật Nhà ở 2023</t>
   </si>
   <si>
-    <t>Người thuê chậm trả tiền chậm. Chủ nhà yêu cầu thêm một khoản phạt nhưng hợp đồng không ghi mức phạt hoặc cách tính</t>
+    <t>Người thuê chậm trả tiền chậm. 
+Chủ nhà yêu cầu thêm một khoản phạt nhưng hợp đồng không ghi mức phạt hoặc cách tính</t>
+  </si>
+  <si>
+    <t>LATE, PAYMENT, DAMAGE</t>
   </si>
   <si>
     <t>B - PEN - 02</t>
   </si>
   <si>
-    <t>Chấm dứt hợp đồng trước hạn và tranh chấp tiền cọc</t>
-  </si>
-  <si>
-    <t>Điều khoản chấm dứt trước hạn không nêu rõ điều kiện chấm dứt, thời hạn báo trước hoặc cách xử lý tiền cọc</t>
-  </si>
-  <si>
-    <t>Điều 328, 428 BLDS 2015
-Điều 172 Luật Nhà ở 2023</t>
-  </si>
-  <si>
-    <t>Người thuê báo chuyển đi trước hạn; chủ nhà giữ toàn bộ tiền cọc nhưng hợp đồng không nói rõ trường hợp này xử lý thế nào.</t>
+    <t>Bị yêu cầu bồi thường cả hao mòn tự nhiên</t>
+  </si>
+  <si>
+    <t>Điều khoản yêu cầu bồi thường mọi hư hỏng nhưng không phân biệt hao mòn tự nhiên với hư hỏng do lỗi của người thuê.</t>
+  </si>
+  <si>
+    <t>Điều 479, 482 BLDS 2015</t>
+  </si>
+  <si>
+    <t>Người thuê có thể phải gánh chi phí sửa chữa hoặc thay mới tài sản không tương xứng với phần thiệt hại do mình gây ra.</t>
+  </si>
+  <si>
+    <t>NATURAL_DAMAGE, COMPSENTATION</t>
   </si>
   <si>
     <t>B - PEN - 03</t>
   </si>
   <si>
-    <t>Bị yêu cầu bồi thường cả hao mòn tự nhiên</t>
-  </si>
-  <si>
-    <t>Điều khoản yêu cầu bồi thường mọi hư hỏng nhưng không phân biệt hao mòn tự nhiên với hư hỏng do lỗi của người thuê.</t>
+    <t>Bị áp dụng mức phạt vi phạm không rõ ràng</t>
+  </si>
+  <si>
+    <t>Hợp đồng không ghi rõ mức phạt hoặc cách tính tiền phạt khi bên B vi phạm nghĩa vụ</t>
+  </si>
+  <si>
+    <t>Chủ nhà tự đưa ra mức phạt sau khi xảy ra vi phạm, dẫn đến tranh chấp số tiền phải trả</t>
+  </si>
+  <si>
+    <t>B - PEN - 04</t>
+  </si>
+  <si>
+    <t>Bị yêu cầu sửa chữa và thay mới tài sản vượt quá thiệt hại thực tế</t>
+  </si>
+  <si>
+    <t>Hợp đồng yêu cầu bên B sửa chữa hoặc thay mới tài sản mà không phân biệt mức độ hư hỏng và giá trị thiệt hại thực tế</t>
+  </si>
+  <si>
+    <t>Người thuê phải chịu chi phí thay mới toàn bộ thiết bị dù chỉ hư hỏng một phần hoặc tài sản đã hao mòn</t>
+  </si>
+  <si>
+    <t>B - PEN - 05</t>
+  </si>
+  <si>
+    <t>Bị phạt do chậm bàn giao nhà không rõ cách tính</t>
+  </si>
+  <si>
+    <t>Khi bàn giao nhà chậm nhưng không xác định rõ thời điểm bàn giao hoặc cách tính số ngày chậm</t>
+  </si>
+  <si>
+    <t>Chủ nhà yêu cầu tiền phạt cho khoảng thời gian hai bên không thống nhất</t>
   </si>
   <si>
     <t>6, ĐĂNG KÝ, CƯ TRÚ &amp; THỦ TỤC HÀNH CHÍNH (RESIDENCE &amp; PROCEDURES)</t>
   </si>
   <si>
-    <t>Điều 479, 482 BLDS 2015</t>
-  </si>
-  <si>
-    <t>Người thuê có thể phải gánh chi phí sửa chữa hoặc thay mới tài sản không tương xứng với phần thiệt hại do mình gây ra.</t>
-  </si>
-  <si>
-    <t>B - PEN - 04</t>
-  </si>
-  <si>
-    <t>Thiếu biên bản bàn giao, danh mục hiện trạng hoặc tài liệu ghi nhận hư hỏng có sẵn trước khi thuê.</t>
-  </si>
-  <si>
-    <t>Người thuê có thể gặp bất lợi khi tranh chấp trách nhiệm sửa chữa, phải tốn thời gian và chi phí chứng minh hoặc khó đòi lại khoản tiền đã bị khấu trừ.</t>
-  </si>
-  <si>
-    <t>A-RES-01</t>
+    <t>A - RES - 01</t>
   </si>
   <si>
     <t>Cho phép người thuê không đăng ký cư trú</t>
@@ -917,14 +1017,22 @@
     <t>Bên B không cần đăng ký cư trú</t>
   </si>
   <si>
-    <t>Điều 27, 30 luật cư trú 2020</t>
+    <t>Điều 27, 30 Luật Cư trú 2020</t>
   </si>
   <si>
     <t>Không lập được hóa đơn cho thuê
-Bị chính quyền phạt</t>
-  </si>
-  <si>
-    <t>A-RES-02</t>
+Bị chính quyền xử phạt</t>
+  </si>
+  <si>
+    <t>RESIDENCE
+ REGISTRATION 
+OBLIGATION 
+COMPLIANCE 
+INVOICE 
+PENALTY</t>
+  </si>
+  <si>
+    <t>A - RES - 02</t>
   </si>
   <si>
     <t>Không thực hiện thông báo lưu trú khi thuộc trách nhiệm</t>
@@ -933,14 +1041,21 @@
     <t>Chủ nhà không xác định ai chịu trách nhiệm thông báo lưu trú</t>
   </si>
   <si>
-    <t>Điều 30 luật cư trú 2020</t>
+    <t>Điều 30 Luật Cư trú 2020</t>
   </si>
   <si>
     <t>Việc thông báo lưu trú có thể bị bỏ sót
 Phát sinh nguy cơ bị xử lý theo quy định áp dụng</t>
   </si>
   <si>
-    <t>A-RES-03</t>
+    <t>RESIDENCE 
+NOTIFICATION 
+OBLIGATION 
+RESPONSIBILITY 
+COMPLIANCE</t>
+  </si>
+  <si>
+    <t>A - RES - 03</t>
   </si>
   <si>
     <t>Thông tin nhà thuê không thống nhất</t>
@@ -949,13 +1064,20 @@
     <t>Thông tin nơi cho thuê trong hợp đồng khác với giấy tờ dùng để đăng ký cư trú</t>
   </si>
   <si>
-    <t>Điều 28 luật cư trú 2020</t>
+    <t>Điều 28 Luật Cư trú 2020</t>
   </si>
   <si>
     <t>Hồ sơ có thể phải xác minh, bổ sung hoặc không được giải quyết nếu không đáp ứng điều kiện</t>
   </si>
   <si>
-    <t>A-RES-04</t>
+    <t>RESIDENCE 
+INFORMATION 
+CONSISTENCY 
+DOCUMENTATION 
+VERIFICATION</t>
+  </si>
+  <si>
+    <t>A - RES - 04</t>
   </si>
   <si>
     <t>Không quy định cách xử lý khi thông tin cư trú thay đổi</t>
@@ -968,10 +1090,15 @@
 Các bên khó xác định ai phải phối hợp xử lý khi phát sinh thủ tục</t>
   </si>
   <si>
-    <t>7, THUẾ, HÓA ĐƠN &amp; NGHĨA VỤ TÀI CHÍNH PHÁP ĐỊNH (TAX &amp; OBLIGATION)</t>
-  </si>
-  <si>
-    <t>B-RES-01</t>
+    <t>RESIDENCE 
+INFORMATION 
+UPDATE 
+NOTIFICATION 
+RESPONSIBILITY 
+OBLIGATION</t>
+  </si>
+  <si>
+    <t>B - RES - 01</t>
   </si>
   <si>
     <t>Thông tin chỗ ở cung cấp cho thủ tục cư trú không chính xác</t>
@@ -983,7 +1110,14 @@
     <t>Các vấn đề liên quan tới cư trú có thể không được giải quyết</t>
   </si>
   <si>
-    <t>B-RES-02</t>
+    <t>RESIDENCE 
+INFORMATION 
+ACCURACY 
+MISMATCH 
+COMPLIANCE</t>
+  </si>
+  <si>
+    <t>B - RES - 02</t>
   </si>
   <si>
     <t>Không có đủ giấy tờ chứng minh chỗ ở hợp pháp</t>
@@ -992,7 +1126,14 @@
     <t>Hồ sơ không có giấy tờ phù hợp để chứng minh chỗ ở hợp pháp hoặc thông tin giấy tờ không khớp</t>
   </si>
   <si>
-    <t>B-RES-03</t>
+    <t>RESIDENCE 
+DOCUMENTATION 
+LEGALITY 
+VERIFICATION 
+COMPLIANCE</t>
+  </si>
+  <si>
+    <t>B - RES - 03</t>
   </si>
   <si>
     <t>Không thực hiện thông báo lưu trú đúng thời hạn</t>
@@ -1005,22 +1146,38 @@
 Việc quản lý thông tin lưu trú không đáp ứng yêu cầu pháp luật</t>
   </si>
   <si>
-    <t>B-RES-04</t>
+    <t>RESIDENCE 
+NOTIFICATION 
+DEADLINE 
+OBLIGATION 
+COMPLIANCE 
+PENALTY</t>
+  </si>
+  <si>
+    <t>B - RES - 04</t>
   </si>
   <si>
     <t>Nhầm lẫn giữa đăng ký tạm trú và thông báo lưu trú</t>
   </si>
   <si>
     <t>Cho rằng hai thủ tục là một hoặc chỉ thực hiện một thủ tục trong mọi trường hợp</t>
-  </si>
-  <si>
-    <t>Điều27, 30 luật cư trú 2020</t>
   </si>
   <si>
     <t>Có thể thực hiện sai hoặc bỏ sót thủ tục cần thiết
 Nguy cơ bị xử lý theo quy định áp dụng</t>
   </si>
   <si>
+    <t>RESIDENCE 
+REGISTRATION 
+NOTIFICATION 
+PROCEDURE 
+COMPLIANCE 
+OBLIGATION</t>
+  </si>
+  <si>
+    <t>7, THUẾ, HÓA ĐƠN &amp; NGHĨA VỤ TÀI CHÍNH PHÁP ĐỊNH (TAX &amp; OBLIGATION)</t>
+  </si>
+  <si>
     <t>A - TAX - 01</t>
   </si>
   <si>
@@ -1030,7 +1187,7 @@
     <t>Thỏa thuận để một phần tiền thuê ngoài hợp đồng nhằm tránh kê khai thuế</t>
   </si>
   <si>
-    <t>Luật Quản lý thuế 108/2025/QH15
+    <t>Điều 17 Luật Quản lý thuế 108/2025/QH15
 Nghị định 68/2026/NĐ-CP</t>
   </si>
   <si>
@@ -1044,6 +1201,10 @@
   </si>
   <si>
     <t>Bên A không phải thực hiện nghĩa vụ thuế hoặc giao nghĩa vụ khai thuế thay trái quy định áp dụng</t>
+  </si>
+  <si>
+    <t>Điều 2, 5, 17 Luật Quản lý thuế 108/2025/QH15
+Điều 4, 8 Nghị định 68/2026/NĐ-CP</t>
   </si>
   <si>
     <t xml:space="preserve">Điều khoản không có tác dụng loại bỏ nghĩa vụ pháp định
@@ -1104,14 +1265,109 @@
     <t>Thiếu quy định về phối hợp khai thuế, nộp thuế thay khi có áp dụng</t>
   </si>
   <si>
-    <t>Hợp đồng có thỏa thuận khai, nộp thuế thay, nhưng chưa làm rõ phạm vi /thông tin cần thiết theo quy định áp dụng</t>
-  </si>
-  <si>
-    <t>Nghị định 68/2026/NĐ-CP
-Thông tư 18/2026/TT-BTC</t>
+    <t>Hợp đồng có thỏa thuận khai, nộp thuế thay, nhưng chưa làm rõ phạm vi/thông tin cần thiết theo quy định áp dụng</t>
+  </si>
+  <si>
+    <t>Điều 8 Nghị định 68/2026/NĐ-CP</t>
   </si>
   <si>
     <t>Khó thực hiện thủ tục, xác định trách nhiệm và đối chiếu khoản thuế</t>
+  </si>
+  <si>
+    <t>B - TAX - 01</t>
+  </si>
+  <si>
+    <t>Không được cam kết xuất hóa đơn hợp lệ</t>
+  </si>
+  <si>
+    <t>Bên B có nghĩa vụ thanh toán nhưng bên A không có nghĩa vụ xuất hóa đơn
+Không gắn điều kiện thanh toán với việc nhận hóa đơn</t>
+  </si>
+  <si>
+    <t>Điều 9, 16, 18 Nghị định 123/2020/NĐ-CP,
+Điều 4 Thông tư 96/2015/TT-BTC</t>
+  </si>
+  <si>
+    <t>Thanh toán nhưng không được nhận hóa đơn hợp lệ/đúng thời điểm
+Không được trừ chi phí thu nhập doanh nghiệp khi tính thuế
+Không được khấu trừ thuế GTGT</t>
+  </si>
+  <si>
+    <t>B - TAX - 02</t>
+  </si>
+  <si>
+    <t>Phải thực hiện nghĩa vụ thuế thay bên A
+Tranh chấp với bên A</t>
+  </si>
+  <si>
+    <t>B - TAX - 03</t>
+  </si>
+  <si>
+    <t>Nộp thuế thay nhưng thiếu nghĩa vụ về hồ sơ/phối hợp của người cho thuê</t>
+  </si>
+  <si>
+    <t>Bên B thực hiện nghĩa vụ đóng thuế thay bên A nhưng bên A không có nghĩa vụ cung cấp hồ sơ thuế</t>
+  </si>
+  <si>
+    <t>Điều 37 Luật Quản lý Thuế 2025,
+Điều 8 Nghị định 68/2026/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Không kê khai/nộp thuế thay đúng hạn do thiếu hồ sơ
+Chịu phạt chậm nộp/vi phạm hành chính về thuế</t>
+  </si>
+  <si>
+    <t>B - TAX - 04</t>
+  </si>
+  <si>
+    <t>Thanh toán vào một tài khoản cá nhân không chính chủ/thanh toán tiền mặt</t>
+  </si>
+  <si>
+    <t>Chỉ định bên B thanh toán vào một tài khoản không phải đại diện/chủ sở hữu bên A
+Cho phép thanh toán tiền mặt với khoản tiền lớn</t>
+  </si>
+  <si>
+    <t>Điều 4 Thông tư 96/2015/TT-BTC,
+Điều 280/283 BLDS 2015,
+Điều 26 Nghị định 181/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Vi phạm quy định chứng từ thanh toán không dùng tiền mặt
+Không được trừ chi phí thu nhập doanh nghiệp khi tính thuế</t>
+  </si>
+  <si>
+    <t>B - TAX - 05</t>
+  </si>
+  <si>
+    <t>Thời điểm xuất hóa đơn lệch so với kỳ thanh toán</t>
+  </si>
+  <si>
+    <t>Bên A chỉ xuất hóa đơn sau khi kết thúc toàn bộ thời hạn thuê
+Bên B phải thanh toán trước theo kỳ</t>
+  </si>
+  <si>
+    <t>Điều 9 Nghị định 123/2020/NĐ-CP,
+Điều 7 Nghị định 70/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Hạch toán xong nhưng vẫn chưa có hóa đơn để kê khai thuê GTGT đúng kỳ
+Trễ hạn kê khai thuế</t>
+  </si>
+  <si>
+    <t>B - TAX - 06</t>
+  </si>
+  <si>
+    <t>Dồn nghĩa vụ nộp phạt hành chính về thuế cho bên thuê</t>
+  </si>
+  <si>
+    <t>Bên B chịu trách nhiệm thanh toán tiền phạt, tiền chậm nộp thuế phát sinh bất kể vi phạm do bên nào gây ra</t>
+  </si>
+  <si>
+    <t>Điều 398, 404 BLDS 2015,
+Điều 3 Nghị định 125/2020/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Phải chịu cả trách nhiệm hành chính do vi phạm của bên A</t>
   </si>
 </sst>
 </file>
@@ -1133,13 +1389,13 @@
     </font>
     <font/>
     <font>
-      <sz val="11.0"/>
+      <b/>
+      <sz val="16.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="16.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -1248,36 +1504,6 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
     </border>
     <border>
       <top style="medium">
@@ -1306,6 +1532,36 @@
       </bottom>
     </border>
     <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -1317,12 +1573,9 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1331,150 +1584,138 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1485,41 +1726,59 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1772,104 +2031,104 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="C4" s="5"/>
-      <c r="O4" s="6"/>
+      <c r="C4" s="4"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="C5" s="5"/>
-      <c r="O5" s="6"/>
+      <c r="C5" s="4"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="5"/>
-      <c r="O6" s="6"/>
+      <c r="C6" s="4"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="5"/>
-      <c r="O7" s="6"/>
+      <c r="C7" s="4"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="5"/>
-      <c r="O8" s="6"/>
+      <c r="C8" s="4"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="5"/>
-      <c r="O9" s="6"/>
+      <c r="C9" s="4"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="5"/>
-      <c r="O10" s="6"/>
+      <c r="C10" s="4"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="5"/>
-      <c r="O11" s="6"/>
+      <c r="C11" s="4"/>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="5"/>
-      <c r="O12" s="6"/>
+      <c r="C12" s="4"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="5"/>
-      <c r="O13" s="6"/>
+      <c r="C13" s="4"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="5"/>
-      <c r="O14" s="6"/>
+      <c r="C14" s="4"/>
+      <c r="O14" s="5"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="5"/>
-      <c r="O15" s="6"/>
+      <c r="C15" s="4"/>
+      <c r="O15" s="5"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="5"/>
-      <c r="O16" s="6"/>
+      <c r="C16" s="4"/>
+      <c r="O16" s="5"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="5"/>
-      <c r="O17" s="6"/>
+      <c r="C17" s="4"/>
+      <c r="O17" s="5"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="5"/>
-      <c r="O18" s="6"/>
+      <c r="C18" s="4"/>
+      <c r="O18" s="5"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="C19" s="5"/>
-      <c r="O19" s="6"/>
+      <c r="C19" s="4"/>
+      <c r="O19" s="5"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="C20" s="5"/>
-      <c r="O20" s="6"/>
+      <c r="C20" s="4"/>
+      <c r="O20" s="5"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="11"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" ht="14.25" customHeight="1"/>
     <row r="23" ht="14.25" customHeight="1"/>
@@ -2874,215 +3133,215 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="C4" s="5"/>
-      <c r="O4" s="6"/>
+      <c r="C4" s="4"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="C5" s="5"/>
-      <c r="O5" s="6"/>
+      <c r="C5" s="4"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="5"/>
-      <c r="O6" s="6"/>
+      <c r="C6" s="4"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="O7" s="6"/>
+      <c r="C7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="6"/>
+      <c r="C8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="O9" s="6"/>
+      <c r="C9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="6"/>
+      <c r="C10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="O11" s="6"/>
+      <c r="C11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="O12" s="6"/>
+      <c r="C12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="6"/>
+      <c r="C13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="O14" s="6"/>
+      <c r="C14" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="5"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="B15" s="10"/>
-      <c r="C15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O15" s="6"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="5"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="B16" s="10"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="11"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="B19" s="10"/>
-      <c r="C19" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15"/>
-      <c r="G19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="G19" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="B20" s="10"/>
-      <c r="C20" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="11"/>
-      <c r="G20" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="G20" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1"/>
@@ -4108,277 +4367,287 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="20" t="s">
-        <v>15</v>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="C7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="22" t="s">
+      <c r="F7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="24" t="s">
+      <c r="G7" s="18" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>29</v>
+      <c r="H7" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>37</v>
+      <c r="F8" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>43</v>
+      <c r="C9" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="30" t="s">
+      <c r="C10" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="C11" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="C12" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="40"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="40"/>
+      <c r="C13" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="31" t="s">
+      <c r="C14" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="C15" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I15" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H14" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" s="40"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="29" t="s">
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="C16" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="30" t="s">
+      <c r="E16" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="32" t="s">
+      <c r="H16" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="44"/>
+      <c r="I16" s="41" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="10"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="10"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
     </row>
     <row r="20" ht="14.25" customHeight="1"/>
     <row r="21" ht="14.25" customHeight="1"/>
@@ -5394,403 +5663,425 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="20" t="s">
-        <v>35</v>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="C7" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="E7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="23" t="s">
+      <c r="G7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="25" t="s">
+      <c r="H7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="C8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="C9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="C10" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="C11" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="26" t="s">
+      <c r="E11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="C12" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="C13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="C14" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="C15" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="26" t="s">
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="C16" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="C17" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="C18" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="C19" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="29" t="s">
+      <c r="H19" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="C20" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="H20" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="39"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="30" t="s">
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="C21" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="36" t="s">
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="C22" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="39" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="39"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="29" t="s">
+      <c r="F22" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="I22" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="39"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="I16" s="39"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="39"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="I18" s="39"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="C19" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="39"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="C20" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I20" s="39"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="C21" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="I21" s="39"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="C22" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="G22" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="47"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="10"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="24"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="10"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="24"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
     </row>
     <row r="26" ht="14.25" customHeight="1"/>
     <row r="27" ht="14.25" customHeight="1"/>
@@ -6800,246 +7091,264 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="20" t="s">
-        <v>144</v>
+      <c r="C3" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>22</v>
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7" s="39"/>
+      <c r="C7" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="32" t="s">
+      <c r="C8" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="C9" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="C10" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="C11" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="C12" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="I8" s="39"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" s="39"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="30" t="s">
+      <c r="H12" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="C13" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="G10" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="I11" s="48"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="I13" s="39"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="I14" s="39"/>
+      <c r="C14" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>185</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="H15" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="I15" s="47"/>
+      <c r="C15" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="H15" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="10"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="10"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
     </row>
     <row r="19" ht="14.25" customHeight="1"/>
     <row r="20" ht="14.25" customHeight="1"/>
@@ -8056,290 +8365,312 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="20" t="s">
-        <v>187</v>
+      <c r="C3" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>22</v>
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="I7" s="50"/>
+      <c r="C7" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="I8" s="39"/>
+      <c r="C8" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="I9" s="39"/>
+      <c r="C9" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="30" t="s">
+      <c r="C10" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="C11" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="C12" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="G10" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>207</v>
-      </c>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="34" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="35" t="s">
+      <c r="H12" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="I12" s="45" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="C13" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G13" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="H11" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="I11" s="48"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="51" t="s">
+      <c r="H13" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="I13" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="31" t="s">
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="C14" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="C15" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="H12" s="52" t="s">
+      <c r="E15" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="51" t="s">
+      <c r="G15" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="H13" s="52" t="s">
+      <c r="H15" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="I15" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="52" t="s">
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="C16" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="51" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="31" t="s">
+      <c r="H16" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F15" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>226</v>
-      </c>
-      <c r="I15" s="39"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" s="31" t="s">
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="C17" s="51" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="E16" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="31" t="s">
+      <c r="G17" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="G16" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="H16" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="I16" s="39"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="53" t="s">
+      <c r="H17" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="D17" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="54" t="s">
-        <v>210</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="H17" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="I17" s="47"/>
     </row>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="10"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="10"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="24"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>
@@ -9352,275 +9683,288 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="20" t="s">
-        <v>234</v>
+      <c r="C3" s="9" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>22</v>
+      <c r="C6" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="51" t="s">
-        <v>235</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="H7" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="I7" s="50"/>
+      <c r="C7" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="61" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="F8" s="62" t="s">
-        <v>243</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="H8" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="I8" s="39"/>
+      <c r="C8" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="H8" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="E9" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>248</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I9" s="39"/>
+      <c r="C9" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="E9" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>271</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="E10" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="H10" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="I10" s="39"/>
+      <c r="C10" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="H10" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="E11" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="I11" s="39"/>
+      <c r="C11" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="63" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>262</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>263</v>
-      </c>
-      <c r="G12" s="64" t="s">
-        <v>264</v>
-      </c>
-      <c r="H12" s="65" t="s">
-        <v>265</v>
-      </c>
-      <c r="I12" s="48"/>
+      <c r="C12" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>291</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="G13" s="57" t="s">
+        <v>296</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="C14" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>300</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="H14" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="C15" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="G15" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="G13" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="H13" s="52" t="s">
-        <v>270</v>
-      </c>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="D14" s="31" t="s">
+      <c r="H15" s="47" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="C16" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="G16" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="E14" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="G14" s="62" t="s">
-        <v>274</v>
-      </c>
-      <c r="H14" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="D15" s="66" t="s">
-        <v>277</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="67" t="s">
-        <v>278</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="H15" s="60" t="s">
-        <v>281</v>
-      </c>
-      <c r="I15" s="39"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="53" t="s">
-        <v>282</v>
-      </c>
-      <c r="D16" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="G16" s="54" t="s">
-        <v>280</v>
-      </c>
-      <c r="H16" s="69" t="s">
-        <v>284</v>
-      </c>
-      <c r="I16" s="47"/>
+      <c r="H16" s="55" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-    </row>
+      <c r="C17" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="D17" s="60" t="s">
+        <v>314</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>315</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
     <row r="20" ht="14.25" customHeight="1"/>
     <row r="21" ht="14.25" customHeight="1"/>
     <row r="22" ht="14.25" customHeight="1"/>
@@ -10594,8 +10938,6 @@
     <row r="990" ht="14.25" customHeight="1"/>
     <row r="991" ht="14.25" customHeight="1"/>
     <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C3:I4"/>
@@ -10629,298 +10971,250 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="20" t="s">
-        <v>279</v>
+      <c r="C3" s="9" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>22</v>
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="70" t="s">
-        <v>287</v>
-      </c>
-      <c r="G7" s="70" t="s">
-        <v>288</v>
-      </c>
-      <c r="H7" s="71" t="s">
-        <v>289</v>
-      </c>
-      <c r="I7" s="50"/>
+      <c r="C7" s="56" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>319</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>320</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="H7" s="64" t="s">
+        <v>322</v>
+      </c>
+      <c r="I7" s="65" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="61" t="s">
-        <v>290</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="62" t="s">
-        <v>292</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="H8" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="I8" s="39"/>
+      <c r="C8" s="56" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>326</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="H8" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="I8" s="65" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="61" t="s">
-        <v>295</v>
-      </c>
-      <c r="D9" s="62" t="s">
-        <v>296</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>297</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>299</v>
-      </c>
-      <c r="I9" s="39"/>
+      <c r="C9" s="56" t="s">
+        <v>330</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>332</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="61" t="s">
-        <v>300</v>
-      </c>
-      <c r="D10" s="62" t="s">
-        <v>301</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>302</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="H10" s="67" t="s">
-        <v>303</v>
-      </c>
-      <c r="I10" s="39"/>
+      <c r="C10" s="66" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="I10" s="65" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="29"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="39"/>
+      <c r="C11" s="56" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="29"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="39"/>
+      <c r="C12" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="I12" s="65" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="39"/>
+      <c r="C13" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>353</v>
+      </c>
+      <c r="I13" s="65" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="34"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="48"/>
+      <c r="C14" s="51" t="s">
+        <v>355</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="G14" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="H14" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="I14" s="65" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="61" t="s">
-        <v>305</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>308</v>
-      </c>
-      <c r="I15" s="39"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="51" t="s">
-        <v>309</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="62" t="s">
-        <v>311</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="H16" s="52" t="s">
-        <v>299</v>
-      </c>
-      <c r="I16" s="39"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="51" t="s">
-        <v>312</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="H17" s="52" t="s">
-        <v>315</v>
-      </c>
-      <c r="I17" s="39"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="62" t="s">
-        <v>318</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="H18" s="52" t="s">
-        <v>320</v>
-      </c>
-      <c r="I18" s="39"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="39"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="39"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="39"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="47"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-    </row>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
     <row r="26" ht="14.25" customHeight="1"/>
     <row r="27" ht="14.25" customHeight="1"/>
     <row r="28" ht="14.25" customHeight="1"/>
@@ -11888,14 +12182,6 @@
     <row r="990" ht="14.25" customHeight="1"/>
     <row r="991" ht="14.25" customHeight="1"/>
     <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C3:I4"/>
@@ -11929,256 +12215,312 @@
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="14.25" customHeight="1"/>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="C3" s="72" t="s">
-        <v>304</v>
+      <c r="C3" s="69" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="C7" s="70" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>362</v>
+      </c>
+      <c r="E7" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="C7" s="73" t="s">
-        <v>321</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="70" t="s">
-        <v>323</v>
-      </c>
-      <c r="G7" s="70" t="s">
-        <v>324</v>
-      </c>
-      <c r="H7" s="71" t="s">
-        <v>325</v>
-      </c>
-      <c r="I7" s="50"/>
+      <c r="F7" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>364</v>
+      </c>
+      <c r="H7" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="I7" s="71"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="C8" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="H8" s="52" t="s">
-        <v>329</v>
-      </c>
-      <c r="I8" s="39"/>
+      <c r="C8" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>370</v>
+      </c>
+      <c r="I8" s="72"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="C9" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>334</v>
-      </c>
-      <c r="I9" s="39"/>
+      <c r="C9" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>375</v>
+      </c>
+      <c r="I9" s="72"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="C10" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="G10" s="62" t="s">
-        <v>338</v>
-      </c>
-      <c r="H10" s="52" t="s">
-        <v>339</v>
-      </c>
-      <c r="I10" s="39"/>
+      <c r="C10" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="G10" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>380</v>
+      </c>
+      <c r="I10" s="72"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="C11" s="51" t="s">
-        <v>340</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="G11" s="62" t="s">
-        <v>343</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>344</v>
-      </c>
-      <c r="I11" s="39"/>
+      <c r="C11" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="G11" s="57" t="s">
+        <v>384</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>385</v>
+      </c>
+      <c r="I11" s="72"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="C12" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>346</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>347</v>
-      </c>
-      <c r="G12" s="64" t="s">
-        <v>348</v>
-      </c>
-      <c r="H12" s="74" t="s">
-        <v>349</v>
-      </c>
-      <c r="I12" s="48"/>
+      <c r="C12" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>387</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>388</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>389</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>390</v>
+      </c>
+      <c r="I12" s="74"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="39"/>
+      <c r="C13" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="I13" s="72"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="39"/>
+      <c r="C14" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="39"/>
+      <c r="C15" s="46" t="s">
+        <v>398</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>402</v>
+      </c>
+      <c r="I15" s="72"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="39"/>
+      <c r="C16" s="46" t="s">
+        <v>403</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="I16" s="72"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="C17" s="29"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="39"/>
+      <c r="C17" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>411</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="I17" s="72"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="39"/>
+      <c r="C18" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>414</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>415</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>416</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>417</v>
+      </c>
+      <c r="I18" s="75"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="39"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="47"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-    </row>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+    </row>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1"/>
     <row r="26" ht="14.25" customHeight="1"/>
@@ -13152,8 +13494,6 @@
     <row r="994" ht="14.25" customHeight="1"/>
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C3:I4"/>
